--- a/Outputs/Scenarios/PtX_demand_CY_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CY_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001515341196766456</v>
+        <v>0.0008210627489166696</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0005051137322554853</v>
+        <v>0.001193154138652529</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005051137322554853</v>
+        <v>0.000511351773708227</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008179046293773275</v>
+        <v>0.00443168195242908</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002726348764591092</v>
+        <v>0.006440043309368465</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002726348764591092</v>
+        <v>0.002760018561157914</v>
       </c>
     </row>
     <row r="43">
